--- a/페이지_내용_엑셀.xlsx
+++ b/페이지_내용_엑셀.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.6" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44.4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -661,45 +661,62 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>구역03 제목</t>
+          <t>구역 순서</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>리깅 포트폴리오</t>
+          <t>슬롯, 진행 방식, 리깅 포폴, 일러스트 포폴, 확인사항, 신청 · 견적, 협업작가</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>화면에 크게 보이는 구역 제목(비우면 기본값)</t>
+          <t>쉼표로 구분. 적은 순서대로 화면에 나오고 번호도 자동으로 바뀝니다</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>구역04 제목</t>
+          <t>구역03 제목</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>일러스트 포트폴리오</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>리깅 포트폴리오</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>화면에 크게 보이는 구역 제목(비우면 기본값)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>구역04 제목</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>일러스트 포트폴리오</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>협업 작가님 할인</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>협업 작가님 할인: 히루네 일러·리깅 각 5만원 / 휘에 일러 5만원 + 표정 2종 + 고가동 리깅 / 벽해류 버츄얼 5만원 + 디자인 할인 (문의 시 적용)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>신청 · 견적 구역 하단 문구</t>
         </is>
